--- a/Compititor's_Price/IKO_Prices/IKO_Prices_11-02-2026.xlsx
+++ b/Compititor's_Price/IKO_Prices/IKO_Prices_11-02-2026.xlsx
@@ -498,27 +498,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='insulation4less.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-25mm-x-2-4m-x-1-2m (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866DFD62D0&gt;, 'Connection to insulation4less.co.uk timed out. (connect timeout=15)'))</t>
+          <t>£10.34</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-25mm-x-2-4m-x-1-2m (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866E108650&gt;, 'Connection to build4less.co.uk timed out. (connect timeout=15)'))</t>
+          <t>£10.34</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.building-supplies-online.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-2-4m-x-1-2m-all-thicknesses (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866D9E8410&gt;, 'Connection to www.building-supplies-online.co.uk timed out. (connect timeout=15)'))</t>
+          <t>£10.34</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.onlineinsulation-sales.com', port=443): Max retries exceeded with url: /product/25mm-iko-enertherm-pir-insulation-board-2400x1200mm/ (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866E10A4D0&gt;, 'Connection to www.onlineinsulation-sales.com timed out. (connect timeout=15)'))</t>
+          <t>£10.57</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationsuperstore.co.uk', port=443): Max retries exceeded with url: /product/iko-enertherm-alu-25mm-universal-rigid-insulation-board-288m2-pallet.html (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866E119D50&gt;, 'Connection to www.insulationsuperstore.co.uk timed out. (connect timeout=15)'))</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,74 +528,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: unknown error: net::ERR_CONNECTION_TIMED_OUT
-  (Session info: chrome=144.0.7559.133)
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff68bcd5715
-	0x7ff68bcd5770
-	0x7ff68ba8108d
-	0x7ff68ba7dbb4
-	0x7ff68ba6e051
-	0x7ff68ba6ff3f
-	0x7ff68ba6e5f1
-	0x7ff68ba6ddbb
-	0x7ff68ba6da71
-	0x7ff68ba6b687
-	0x7ff68ba6be02
-	0x7ff68ba85336
-	0x7ff68bb2aca4
-	0x7ff68bb0598a
-	0x7ff68bb29e45
-	0x7ff68baccc28
-	0x7ff68bacdb33
-	0x7ff68bfbe9f0
-	0x7ff68bfb8ded
-	0x7ff68bfd969a
-	0x7ff68bcf11e5
-	0x7ff68bcf99cc
-	0x7ff68bcdebf4
-	0x7ff68bcdeda6
-	0x7ff68bcc4e87
-	0x7ffd1353e8d7
-	0x7ffd14e2c53c
-</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: unknown error: net::ERR_CONNECTION_TIMED_OUT
-  (Session info: chrome=144.0.7559.133)
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff68bcd5715
-	0x7ff68bcd5770
-	0x7ff68ba8108d
-	0x7ff68ba7dbb4
-	0x7ff68ba6e051
-	0x7ff68ba6ff3f
-	0x7ff68ba6e5f1
-	0x7ff68ba6ddbb
-	0x7ff68ba6da71
-	0x7ff68ba6b687
-	0x7ff68ba6be02
-	0x7ff68ba85336
-	0x7ff68bb2aca4
-	0x7ff68bb0598a
-	0x7ff68bb29e45
-	0x7ff68baccc28
-	0x7ff68bacdb33
-	0x7ff68bfbe9f0
-	0x7ff68bfb8ded
-	0x7ff68bfd969a
-	0x7ff68bcf11e5
-	0x7ff68bcf99cc
-	0x7ff68bcdebf4
-	0x7ff68bcdeda6
-	0x7ff68bcc4e87
-	0x7ffd1353e8d7
-	0x7ffd14e2c53c
-</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -617,27 +555,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='insulation4less.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-30mm-x-2-4m-x-1-2m (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866E147290&gt;, 'Connection to insulation4less.co.uk timed out. (connect timeout=15)'))</t>
+          <t>£12.09</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-30mm-x-2-4m-x-1-2m (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866E11B190&gt;, 'Connection to build4less.co.uk timed out. (connect timeout=15)'))</t>
+          <t>£12.09</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.building-supplies-online.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-2-4m-x-1-2m-all-thicknesses?variant=55643414004096 (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866E118510&gt;, 'Connection to www.building-supplies-online.co.uk timed out. (connect timeout=15)'))</t>
+          <t>£12.09</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.onlineinsulation-sales.com', port=443): Max retries exceeded with url: /product/30mm-iko-enertherm-pir-insulation-board-2400x1200mm/ (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866DFD47D0&gt;, 'Connection to www.onlineinsulation-sales.com timed out. (connect timeout=15)'))</t>
+          <t>£12.09</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationsuperstore.co.uk', port=443): Max retries exceeded with url: /product/iko-enertherm-alu-30mm-universal-rigid-insulation-board-230-4m2-pallet.html (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866E10B250&gt;, 'Connection to www.insulationsuperstore.co.uk timed out. (connect timeout=15)'))</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -647,79 +585,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: unknown error: net::ERR_CONNECTION_TIMED_OUT
-  (Session info: chrome=144.0.7559.133)
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff68bcd5715
-	0x7ff68bcd5770
-	0x7ff68ba8108d
-	0x7ff68ba7dbb4
-	0x7ff68ba6e051
-	0x7ff68ba6ff3f
-	0x7ff68ba6e5f1
-	0x7ff68ba6ddbb
-	0x7ff68ba6da71
-	0x7ff68ba6b687
-	0x7ff68ba6be02
-	0x7ff68ba85336
-	0x7ff68bb2aca4
-	0x7ff68bb0598a
-	0x7ff68bb29e45
-	0x7ff68baccc28
-	0x7ff68bacdb33
-	0x7ff68bfbe9f0
-	0x7ff68bfb8ded
-	0x7ff68bfd969a
-	0x7ff68bcf11e5
-	0x7ff68bcf99cc
-	0x7ff68bcdebf4
-	0x7ff68bcdeda6
-	0x7ff68bcc4e87
-	0x7ffd1353e8d7
-	0x7ffd14e2c53c
-</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: unknown error: net::ERR_CONNECTION_TIMED_OUT
-  (Session info: chrome=144.0.7559.133)
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff68bcd5715
-	0x7ff68bcd5770
-	0x7ff68ba8108d
-	0x7ff68ba7dbb4
-	0x7ff68ba6e051
-	0x7ff68ba6ff3f
-	0x7ff68ba6e5f1
-	0x7ff68ba6ddbb
-	0x7ff68ba6da71
-	0x7ff68ba6b687
-	0x7ff68ba6be02
-	0x7ff68ba85336
-	0x7ff68bb2aca4
-	0x7ff68bb0598a
-	0x7ff68bb29e45
-	0x7ff68baccc28
-	0x7ff68bacdb33
-	0x7ff68bfbe9f0
-	0x7ff68bfb8ded
-	0x7ff68bfd969a
-	0x7ff68bcf11e5
-	0x7ff68bcf99cc
-	0x7ff68bcdebf4
-	0x7ff68bcdeda6
-	0x7ff68bcc4e87
-	0x7ffd1353e8d7
-	0x7ffd14e2c53c
-</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /30mm-iko-enertherm-alu-pir-rigid-insulation-board-1200mm-x-2400mm-pack-of-16.html (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866E1453D0&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=15)'))</t>
+          <t>POA</t>
         </is>
       </c>
     </row>
@@ -736,27 +612,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='insulation4less.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-40mm-x-2-4m-x-1-2m (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866E144610&gt;, 'Connection to insulation4less.co.uk timed out. (connect timeout=15)'))</t>
+          <t>£15.26</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-40mm-x-2-4m-x-1-2m (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866E109C10&gt;, 'Connection to build4less.co.uk timed out. (connect timeout=15)'))</t>
+          <t>£15.26</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.building-supplies-online.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-2-4m-x-1-2m-all-thicknesses?variant=55643414036864 (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866DFD4ED0&gt;, 'Connection to www.building-supplies-online.co.uk timed out. (connect timeout=15)'))</t>
+          <t>£15.26</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.onlineinsulation-sales.com', port=443): Max retries exceeded with url: /product/40mm-iko-enertherm-pir-insulation-board-2400x1200mm/ (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866E11B4D0&gt;, 'Connection to www.onlineinsulation-sales.com timed out. (connect timeout=15)'))</t>
+          <t>£15.27</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationsuperstore.co.uk', port=443): Max retries exceeded with url: /product/iko-enertherm-alu-40mm-universal-rigid-insulation-board-172-8m2-pallet.html (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866E0EC890&gt;, 'Connection to www.insulationsuperstore.co.uk timed out. (connect timeout=15)'))</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -766,79 +642,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: unknown error: net::ERR_CONNECTION_TIMED_OUT
-  (Session info: chrome=144.0.7559.133)
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff68bcd5715
-	0x7ff68bcd5770
-	0x7ff68ba8108d
-	0x7ff68ba7dbb4
-	0x7ff68ba6e051
-	0x7ff68ba6ff3f
-	0x7ff68ba6e5f1
-	0x7ff68ba6ddbb
-	0x7ff68ba6da71
-	0x7ff68ba6b687
-	0x7ff68ba6be02
-	0x7ff68ba85336
-	0x7ff68bb2aca4
-	0x7ff68bb0598a
-	0x7ff68bb29e45
-	0x7ff68baccc28
-	0x7ff68bacdb33
-	0x7ff68bfbe9f0
-	0x7ff68bfb8ded
-	0x7ff68bfd969a
-	0x7ff68bcf11e5
-	0x7ff68bcf99cc
-	0x7ff68bcdebf4
-	0x7ff68bcdeda6
-	0x7ff68bcc4e87
-	0x7ffd1353e8d7
-	0x7ffd14e2c53c
-</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: unknown error: net::ERR_CONNECTION_TIMED_OUT
-  (Session info: chrome=144.0.7559.133)
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff68bcd5715
-	0x7ff68bcd5770
-	0x7ff68ba8108d
-	0x7ff68ba7dbb4
-	0x7ff68ba6e051
-	0x7ff68ba6ff3f
-	0x7ff68ba6e5f1
-	0x7ff68ba6ddbb
-	0x7ff68ba6da71
-	0x7ff68ba6b687
-	0x7ff68ba6be02
-	0x7ff68ba85336
-	0x7ff68bb2aca4
-	0x7ff68bb0598a
-	0x7ff68bb29e45
-	0x7ff68baccc28
-	0x7ff68bacdb33
-	0x7ff68bfbe9f0
-	0x7ff68bfb8ded
-	0x7ff68bfd969a
-	0x7ff68bcf11e5
-	0x7ff68bcf99cc
-	0x7ff68bcdebf4
-	0x7ff68bcdeda6
-	0x7ff68bcc4e87
-	0x7ffd1353e8d7
-	0x7ffd14e2c53c
-</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /40mm-iko-enertherm-alu-pir-rigid-insulation-board-1200mm-x-2400mm-pack-of-12.html (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866E118410&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=15)'))</t>
+          <t>POA</t>
         </is>
       </c>
     </row>
@@ -855,27 +669,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='insulation4less.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-50mm-x-2-4m-x-1-2m (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866E118450&gt;, 'Connection to insulation4less.co.uk timed out. (connect timeout=15)'))</t>
+          <t>£15.86</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-50mm-x-2-4m-x-1-2m (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866E10BAD0&gt;, 'Connection to build4less.co.uk timed out. (connect timeout=15)'))</t>
+          <t>£15.86</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.building-supplies-online.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-2-4m-x-1-2m-all-thicknesses?variant=55643414069632 (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866E146B50&gt;, 'Connection to www.building-supplies-online.co.uk timed out. (connect timeout=15)'))</t>
+          <t>£15.86</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.onlineinsulation-sales.com', port=443): Max retries exceeded with url: /product/50mm-iko-enertherm-pir-insulation-board-2400x1200mm/ (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866E0EDD90&gt;, 'Connection to www.onlineinsulation-sales.com timed out. (connect timeout=15)'))</t>
+          <t>£15.86</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationsuperstore.co.uk', port=443): Max retries exceeded with url: /product/iko-enertherm-alu-50mm-universal-rigid-insulation-board-144m2-pallet.html (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866E108490&gt;, 'Connection to www.insulationsuperstore.co.uk timed out. (connect timeout=15)'))</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -885,79 +699,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: unknown error: net::ERR_CONNECTION_TIMED_OUT
-  (Session info: chrome=144.0.7559.133)
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff68bcd5715
-	0x7ff68bcd5770
-	0x7ff68ba8108d
-	0x7ff68ba7dbb4
-	0x7ff68ba6e051
-	0x7ff68ba6ff3f
-	0x7ff68ba6e5f1
-	0x7ff68ba6ddbb
-	0x7ff68ba6da71
-	0x7ff68ba6b687
-	0x7ff68ba6be02
-	0x7ff68ba85336
-	0x7ff68bb2aca4
-	0x7ff68bb0598a
-	0x7ff68bb29e45
-	0x7ff68baccc28
-	0x7ff68bacdb33
-	0x7ff68bfbe9f0
-	0x7ff68bfb8ded
-	0x7ff68bfd969a
-	0x7ff68bcf11e5
-	0x7ff68bcf99cc
-	0x7ff68bcdebf4
-	0x7ff68bcdeda6
-	0x7ff68bcc4e87
-	0x7ffd1353e8d7
-	0x7ffd14e2c53c
-</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: unknown error: net::ERR_CONNECTION_TIMED_OUT
-  (Session info: chrome=144.0.7559.133)
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff68bcd5715
-	0x7ff68bcd5770
-	0x7ff68ba8108d
-	0x7ff68ba7dbb4
-	0x7ff68ba6e051
-	0x7ff68ba6ff3f
-	0x7ff68ba6e5f1
-	0x7ff68ba6ddbb
-	0x7ff68ba6da71
-	0x7ff68ba6b687
-	0x7ff68ba6be02
-	0x7ff68ba85336
-	0x7ff68bb2aca4
-	0x7ff68bb0598a
-	0x7ff68bb29e45
-	0x7ff68baccc28
-	0x7ff68bacdb33
-	0x7ff68bfbe9f0
-	0x7ff68bfb8ded
-	0x7ff68bfd969a
-	0x7ff68bcf11e5
-	0x7ff68bcf99cc
-	0x7ff68bcdebf4
-	0x7ff68bcdeda6
-	0x7ff68bcc4e87
-	0x7ffd1353e8d7
-	0x7ffd14e2c53c
-</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /50mm-iko-enertherm-alu-pir-rigid-insulation-board-1200mm-x-2400mm-pack-of-10.html (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866DFD7450&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=15)'))</t>
+          <t>POA</t>
         </is>
       </c>
     </row>
@@ -974,27 +726,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='insulation4less.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-60mm-x-2-4m-x-1-2m (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866E1471D0&gt;, 'Connection to insulation4less.co.uk timed out. (connect timeout=15)'))</t>
+          <t>£19.70</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-60mm-x-2-4m-x-1-2m (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866E11AB10&gt;, 'Connection to build4less.co.uk timed out. (connect timeout=15)'))</t>
+          <t>£19.70</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.building-supplies-online.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-2-4m-x-1-2m-all-thicknesses?variant=55643414102400 (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866E130DD0&gt;, 'Connection to www.building-supplies-online.co.uk timed out. (connect timeout=15)'))</t>
+          <t>£19.70</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.onlineinsulation-sales.com', port=443): Max retries exceeded with url: /product/60mm-iko-enertherm-pir-insulation-board-2400x1200mm/ (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866E1462D0&gt;, 'Connection to www.onlineinsulation-sales.com timed out. (connect timeout=15)'))</t>
+          <t>£19.78</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationsuperstore.co.uk', port=443): Max retries exceeded with url: /product/iko-enertherm-alu-60mm-universal-rigid-insulation-board-115-2m2-pallet.html (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866DFD79D0&gt;, 'Connection to www.insulationsuperstore.co.uk timed out. (connect timeout=15)'))</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1004,79 +756,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: unknown error: net::ERR_CONNECTION_TIMED_OUT
-  (Session info: chrome=144.0.7559.133)
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff68bcd5715
-	0x7ff68bcd5770
-	0x7ff68ba8108d
-	0x7ff68ba7dbb4
-	0x7ff68ba6e051
-	0x7ff68ba6ff3f
-	0x7ff68ba6e5f1
-	0x7ff68ba6ddbb
-	0x7ff68ba6da71
-	0x7ff68ba6b687
-	0x7ff68ba6be02
-	0x7ff68ba85336
-	0x7ff68bb2aca4
-	0x7ff68bb0598a
-	0x7ff68bb29e45
-	0x7ff68baccc28
-	0x7ff68bacdb33
-	0x7ff68bfbe9f0
-	0x7ff68bfb8ded
-	0x7ff68bfd969a
-	0x7ff68bcf11e5
-	0x7ff68bcf99cc
-	0x7ff68bcdebf4
-	0x7ff68bcdeda6
-	0x7ff68bcc4e87
-	0x7ffd1353e8d7
-	0x7ffd14e2c53c
-</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: unknown error: net::ERR_CONNECTION_TIMED_OUT
-  (Session info: chrome=144.0.7559.133)
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff68bcd5715
-	0x7ff68bcd5770
-	0x7ff68ba8108d
-	0x7ff68ba7dbb4
-	0x7ff68ba6e051
-	0x7ff68ba6ff3f
-	0x7ff68ba6e5f1
-	0x7ff68ba6ddbb
-	0x7ff68ba6da71
-	0x7ff68ba6b687
-	0x7ff68ba6be02
-	0x7ff68ba85336
-	0x7ff68bb2aca4
-	0x7ff68bb0598a
-	0x7ff68bb29e45
-	0x7ff68baccc28
-	0x7ff68bacdb33
-	0x7ff68bfbe9f0
-	0x7ff68bfb8ded
-	0x7ff68bfd969a
-	0x7ff68bcf11e5
-	0x7ff68bcf99cc
-	0x7ff68bcdebf4
-	0x7ff68bcdeda6
-	0x7ff68bcc4e87
-	0x7ffd1353e8d7
-	0x7ffd14e2c53c
-</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /60mm-iko-enertherm-alu-pir-rigid-insulation-board-1200mm-x-2400mm-pack-of-8.html (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866E11A210&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=15)'))</t>
+          <t>POA</t>
         </is>
       </c>
     </row>
@@ -1093,27 +783,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='insulation4less.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-70mm-x-2-4m-x-1-2m (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866E109390&gt;, 'Connection to insulation4less.co.uk timed out. (connect timeout=15)'))</t>
+          <t>£22.05</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-70mm-x-2-4m-x-1-2m (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866E132490&gt;, 'Connection to build4less.co.uk timed out. (connect timeout=15)'))</t>
+          <t>£22.05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.building-supplies-online.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-2-4m-x-1-2m-all-thicknesses?variant=55643414135168 (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866E11A8D0&gt;, 'Connection to www.building-supplies-online.co.uk timed out. (connect timeout=15)'))</t>
+          <t>£22.05</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.onlineinsulation-sales.com', port=443): Max retries exceeded with url: /product/70mm-iko-enertherm-pir-insulation-board-2400x1200mm/ (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866E11B3D0&gt;, 'Connection to www.onlineinsulation-sales.com timed out. (connect timeout=15)'))</t>
+          <t>£22.06</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationsuperstore.co.uk', port=443): Max retries exceeded with url: /product/iko-enertherm-alu-70mm-universal-rigid-insulation-board-100-8m2-pallet.html (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866E10A750&gt;, 'Connection to www.insulationsuperstore.co.uk timed out. (connect timeout=15)'))</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1123,79 +813,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: unknown error: net::ERR_CONNECTION_TIMED_OUT
-  (Session info: chrome=144.0.7559.133)
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff68bcd5715
-	0x7ff68bcd5770
-	0x7ff68ba8108d
-	0x7ff68ba7dbb4
-	0x7ff68ba6e051
-	0x7ff68ba6ff3f
-	0x7ff68ba6e5f1
-	0x7ff68ba6ddbb
-	0x7ff68ba6da71
-	0x7ff68ba6b687
-	0x7ff68ba6be02
-	0x7ff68ba85336
-	0x7ff68bb2aca4
-	0x7ff68bb0598a
-	0x7ff68bb29e45
-	0x7ff68baccc28
-	0x7ff68bacdb33
-	0x7ff68bfbe9f0
-	0x7ff68bfb8ded
-	0x7ff68bfd969a
-	0x7ff68bcf11e5
-	0x7ff68bcf99cc
-	0x7ff68bcdebf4
-	0x7ff68bcdeda6
-	0x7ff68bcc4e87
-	0x7ffd1353e8d7
-	0x7ffd14e2c53c
-</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: unknown error: net::ERR_CONNECTION_TIMED_OUT
-  (Session info: chrome=144.0.7559.133)
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff68bcd5715
-	0x7ff68bcd5770
-	0x7ff68ba8108d
-	0x7ff68ba7dbb4
-	0x7ff68ba6e051
-	0x7ff68ba6ff3f
-	0x7ff68ba6e5f1
-	0x7ff68ba6ddbb
-	0x7ff68ba6da71
-	0x7ff68ba6b687
-	0x7ff68ba6be02
-	0x7ff68ba85336
-	0x7ff68bb2aca4
-	0x7ff68bb0598a
-	0x7ff68bb29e45
-	0x7ff68baccc28
-	0x7ff68bacdb33
-	0x7ff68bfbe9f0
-	0x7ff68bfb8ded
-	0x7ff68bfd969a
-	0x7ff68bcf11e5
-	0x7ff68bcf99cc
-	0x7ff68bcdebf4
-	0x7ff68bcdeda6
-	0x7ff68bcc4e87
-	0x7ffd1353e8d7
-	0x7ffd14e2c53c
-</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /70mm-iko-enertherm-alu-pir-rigid-insulation-board-1200mm-x-2400mm-pack-of-7.html (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866DFD4E10&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=15)'))</t>
+          <t>POA</t>
         </is>
       </c>
     </row>
@@ -1212,27 +840,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='insulation4less.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-75mm-x-2-4m-x-1-2m (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866E114B50&gt;, 'Connection to insulation4less.co.uk timed out. (connect timeout=15)'))</t>
+          <t>£22.11</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-75mm-x-2-4m-x-1-2m (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866E145C50&gt;, 'Connection to build4less.co.uk timed out. (connect timeout=15)'))</t>
+          <t>£22.11</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.building-supplies-online.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-2-4m-x-1-2m-all-thicknesses?variant=55643414167936 (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866DFD7210&gt;, 'Connection to www.building-supplies-online.co.uk timed out. (connect timeout=15)'))</t>
+          <t>£22.11</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.onlineinsulation-sales.com', port=443): Max retries exceeded with url: /product/75mm-iko-enertherm-pir-insulation-board-2400x1200mm/ (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866E108F50&gt;, 'Connection to www.onlineinsulation-sales.com timed out. (connect timeout=15)'))</t>
+          <t>£22.13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationsuperstore.co.uk', port=443): Max retries exceeded with url: /product/iko-enertherm-alu-75mm-universal-rigid-insulation-board-92-16m2-pallet.html (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866E117B10&gt;, 'Connection to www.insulationsuperstore.co.uk timed out. (connect timeout=15)'))</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1242,74 +870,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: unknown error: net::ERR_CONNECTION_TIMED_OUT
-  (Session info: chrome=144.0.7559.133)
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff68bcd5715
-	0x7ff68bcd5770
-	0x7ff68ba8108d
-	0x7ff68ba7dbb4
-	0x7ff68ba6e051
-	0x7ff68ba6ff3f
-	0x7ff68ba6e5f1
-	0x7ff68ba6ddbb
-	0x7ff68ba6da71
-	0x7ff68ba6b687
-	0x7ff68ba6be02
-	0x7ff68ba85336
-	0x7ff68bb2aca4
-	0x7ff68bb0598a
-	0x7ff68bb29e45
-	0x7ff68baccc28
-	0x7ff68bacdb33
-	0x7ff68bfbe9f0
-	0x7ff68bfb8ded
-	0x7ff68bfd969a
-	0x7ff68bcf11e5
-	0x7ff68bcf99cc
-	0x7ff68bcdebf4
-	0x7ff68bcdeda6
-	0x7ff68bcc4e87
-	0x7ffd1353e8d7
-	0x7ffd14e2c53c
-</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: unknown error: net::ERR_CONNECTION_TIMED_OUT
-  (Session info: chrome=144.0.7559.133)
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff68bcd5715
-	0x7ff68bcd5770
-	0x7ff68ba8108d
-	0x7ff68ba7dbb4
-	0x7ff68ba6e051
-	0x7ff68ba6ff3f
-	0x7ff68ba6e5f1
-	0x7ff68ba6ddbb
-	0x7ff68ba6da71
-	0x7ff68ba6b687
-	0x7ff68ba6be02
-	0x7ff68ba85336
-	0x7ff68bb2aca4
-	0x7ff68bb0598a
-	0x7ff68bb29e45
-	0x7ff68baccc28
-	0x7ff68bacdb33
-	0x7ff68bfbe9f0
-	0x7ff68bfb8ded
-	0x7ff68bfd969a
-	0x7ff68bcf11e5
-	0x7ff68bcf99cc
-	0x7ff68bcdebf4
-	0x7ff68bcdeda6
-	0x7ff68bcc4e87
-	0x7ffd1353e8d7
-	0x7ffd14e2c53c
-</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1331,27 +897,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='insulation4less.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-80mm-x-2-4m-x-1-2m (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866DF35BD0&gt;, 'Connection to insulation4less.co.uk timed out. (connect timeout=15)'))</t>
+          <t>£25.10</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-80mm-x-2-4m-x-1-2m (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866E124690&gt;, 'Connection to build4less.co.uk timed out. (connect timeout=15)'))</t>
+          <t>£25.10</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.building-supplies-online.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-2-4m-x-1-2m-all-thicknesses?variant=55643414200704 (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866E119DD0&gt;, 'Connection to www.building-supplies-online.co.uk timed out. (connect timeout=15)'))</t>
+          <t>£25.10</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.onlineinsulation-sales.com', port=443): Max retries exceeded with url: /product/80mm-iko-enertherm-pir-insulation-board-2400x1200mm/ (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866E0EED50&gt;, 'Connection to www.onlineinsulation-sales.com timed out. (connect timeout=15)'))</t>
+          <t>£25.48</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationsuperstore.co.uk', port=443): Max retries exceeded with url: /product/iko-enertherm-alu-80mm-universal-rigid-insulation-board-86-4m2-pallet.html (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866DFD4410&gt;, 'Connection to www.insulationsuperstore.co.uk timed out. (connect timeout=15)'))</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1361,79 +927,17 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: unknown error: net::ERR_CONNECTION_TIMED_OUT
-  (Session info: chrome=144.0.7559.133)
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff68bcd5715
-	0x7ff68bcd5770
-	0x7ff68ba8108d
-	0x7ff68ba7dbb4
-	0x7ff68ba6e051
-	0x7ff68ba6ff3f
-	0x7ff68ba6e5f1
-	0x7ff68ba6ddbb
-	0x7ff68ba6da71
-	0x7ff68ba6b687
-	0x7ff68ba6be02
-	0x7ff68ba85336
-	0x7ff68bb2aca4
-	0x7ff68bb0598a
-	0x7ff68bb29e45
-	0x7ff68baccc28
-	0x7ff68bacdb33
-	0x7ff68bfbe9f0
-	0x7ff68bfb8ded
-	0x7ff68bfd969a
-	0x7ff68bcf11e5
-	0x7ff68bcf99cc
-	0x7ff68bcdebf4
-	0x7ff68bcdeda6
-	0x7ff68bcc4e87
-	0x7ffd1353e8d7
-	0x7ffd14e2c53c
-</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: unknown error: net::ERR_CONNECTION_TIMED_OUT
-  (Session info: chrome=144.0.7559.133)
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff68bcd5715
-	0x7ff68bcd5770
-	0x7ff68ba8108d
-	0x7ff68ba7dbb4
-	0x7ff68ba6e051
-	0x7ff68ba6ff3f
-	0x7ff68ba6e5f1
-	0x7ff68ba6ddbb
-	0x7ff68ba6da71
-	0x7ff68ba6b687
-	0x7ff68ba6be02
-	0x7ff68ba85336
-	0x7ff68bb2aca4
-	0x7ff68bb0598a
-	0x7ff68bb29e45
-	0x7ff68baccc28
-	0x7ff68bacdb33
-	0x7ff68bfbe9f0
-	0x7ff68bfb8ded
-	0x7ff68bfd969a
-	0x7ff68bcf11e5
-	0x7ff68bcf99cc
-	0x7ff68bcdebf4
-	0x7ff68bcdeda6
-	0x7ff68bcc4e87
-	0x7ffd1353e8d7
-	0x7ffd14e2c53c
-</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /80mm-iko-enertherm-alu-pir-rigid-insulation-board-1200mm-x-2400mm-pack-of-6.html (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866E146E50&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=15)'))</t>
+          <t>POA</t>
         </is>
       </c>
     </row>
@@ -1450,27 +954,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='insulation4less.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-90mm-x-2-4m-x-1-2m (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866E1271D0&gt;, 'Connection to insulation4less.co.uk timed out. (connect timeout=15)'))</t>
+          <t>£27.67</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-90mm-x-2-4m-x-1-2m (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866E10AD10&gt;, 'Connection to build4less.co.uk timed out. (connect timeout=15)'))</t>
+          <t>£27.67</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.building-supplies-online.co.uk', port=443): Max retries exceeded with url: /products/iko-enertherm-alu-2-4m-x-1-2m-all-thicknesses?variant=55643414233472 (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866E119410&gt;, 'Connection to www.building-supplies-online.co.uk timed out. (connect timeout=15)'))</t>
+          <t>£27.67</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.onlineinsulation-sales.com', port=443): Max retries exceeded with url: /product/90mm-iko-enertherm-pir-insulation-board-2400x1200mm/ (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866E1333D0&gt;, 'Connection to www.onlineinsulation-sales.com timed out. (connect timeout=15)'))</t>
+          <t>£27.69</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationsuperstore.co.uk', port=443): Max retries exceeded with url: /product/iko-enertherm-alu-90mm-universal-rigid-insulation-board-80-64m2-pallet.html (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000001866E117BD0&gt;, 'Connection to www.insulationsuperstore.co.uk timed out. (connect timeout=15)'))</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1480,38 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: unknown error: net::ERR_CONNECTION_TIMED_OUT
-  (Session info: chrome=144.0.7559.133)
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff68bcd5715
-	0x7ff68bcd5770
-	0x7ff68ba8108d
-	0x7ff68ba7dbb4
-	0x7ff68ba6e051
-	0x7ff68ba6ff3f
-	0x7ff68ba6e5f1
-	0x7ff68ba6ddbb
-	0x7ff68ba6da71
-	0x7ff68ba6b687
-	0x7ff68ba6be02
-	0x7ff68ba85336
-	0x7ff68bb2aca4
-	0x7ff68bb0598a
-	0x7ff68bb29e45
-	0x7ff68baccc28
-	0x7ff68bacdb33
-	0x7ff68bfbe9f0
-	0x7ff68bfb8ded
-	0x7ff68bfd969a
-	0x7ff68bcf11e5
-	0x7ff68bcf99cc
-	0x7ff68bcdebf4
-	0x7ff68bcdeda6
-	0x7ff68bcc4e87
-	0x7ffd1353e8d7
-	0x7ffd14e2c53c
-</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
